--- a/outputs/resultados_estacionalidad_comprobacion.xlsx
+++ b/outputs/resultados_estacionalidad_comprobacion.xlsx
@@ -640,19 +640,19 @@
         <v>218</v>
       </c>
       <c r="C9" t="n">
-        <v>1.197855203193335e-28</v>
+        <v>2.638197803720992</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0.003563164707518478</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>No rechazar H0</t>
+          <t>Rechazar H0</t>
         </is>
       </c>
     </row>
@@ -692,19 +692,19 @@
         <v>218</v>
       </c>
       <c r="C11" t="n">
-        <v>8.084253429069964e-29</v>
+        <v>2.736185012107882</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0.002535507330298936</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>No rechazar H0</t>
+          <t>Rechazar H0</t>
         </is>
       </c>
     </row>
